--- a/construction_template/data/templates_blank/test_control.xlsx
+++ b/construction_template/data/templates_blank/test_control.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="97">
   <si>
-    <t xml:space="preserve">臺北市政府工務局水利工程處</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">材料設備送審管制總表</t>
@@ -56,7 +56,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">任泰水利技師事務所</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
@@ -492,7 +492,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">臺北市政府工務局水利工程處
+    <t xml:space="preserve">
 各階段抽查施工作業紀錄統計表</t>
   </si>
   <si>
@@ -559,7 +559,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">104</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -568,7 +568,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -578,7 +578,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -587,7 +587,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -597,7 +597,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">25</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -606,14 +606,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
     <t xml:space="preserve">契約編號</t>
   </si>
   <si>
-    <t xml:space="preserve">H-104-04-104042</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">竣工日期</t>
@@ -627,7 +627,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">104</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -636,7 +636,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -646,7 +646,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -655,7 +655,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -665,7 +665,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -674,20 +674,20 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
     <t xml:space="preserve">監造單位</t>
   </si>
   <si>
-    <t xml:space="preserve">任泰水利技師事務所</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">施工廠商</t>
   </si>
   <si>
-    <t xml:space="preserve">豐松營造有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">施工抽查項目</t>

--- a/construction_template/data/templates_blank/test_control.xlsx
+++ b/construction_template/data/templates_blank/test_control.xlsx
@@ -492,8 +492,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">
-各階段抽查施工作業紀錄統計表</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">工程名稱</t>
@@ -559,7 +558,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">104</t>
     </r>
     <r>
       <rPr>
@@ -568,7 +567,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">年</t>
     </r>
     <r>
       <rPr>
@@ -578,7 +577,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">5</t>
     </r>
     <r>
       <rPr>
@@ -587,7 +586,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">月</t>
     </r>
     <r>
       <rPr>
@@ -597,7 +596,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">25</t>
     </r>
     <r>
       <rPr>
@@ -606,7 +605,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">日</t>
     </r>
   </si>
   <si>
@@ -627,7 +626,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">104</t>
     </r>
     <r>
       <rPr>
@@ -636,7 +635,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">年</t>
     </r>
     <r>
       <rPr>
@@ -646,7 +645,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">8</t>
     </r>
     <r>
       <rPr>
@@ -655,7 +654,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">月</t>
     </r>
     <r>
       <rPr>
@@ -665,7 +664,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">11</t>
     </r>
     <r>
       <rPr>
@@ -674,7 +673,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t xml:space="preserve">日</t>
     </r>
   </si>
   <si>
@@ -1726,7 +1725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1912,7 +1911,7 @@
       <c r="O7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12"/>
       <c r="D8" s="13" t="s">
@@ -1956,7 +1955,7 @@
       <c r="O9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="18"/>
       <c r="D10" s="13" t="s">
@@ -2000,7 +1999,7 @@
       <c r="O11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
       <c r="D12" s="13" t="s">
@@ -2042,7 +2041,7 @@
       <c r="O13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
       <c r="D14" s="13" t="s">
@@ -2084,7 +2083,7 @@
       <c r="O15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="18"/>
       <c r="D16" s="13" t="s">
@@ -2128,7 +2127,7 @@
       <c r="O17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="18"/>
       <c r="D18" s="13"/>
@@ -2162,7 +2161,7 @@
       <c r="O19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="18"/>
       <c r="D20" s="13"/>
@@ -2196,7 +2195,7 @@
       <c r="O21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="n"/>
+      <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="18"/>
       <c r="D22" s="13"/>
@@ -2230,7 +2229,7 @@
       <c r="O23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n"/>
+      <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="18"/>
       <c r="D24" s="13"/>
@@ -2264,7 +2263,7 @@
       <c r="O25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n"/>
+      <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="18"/>
       <c r="D26" s="13"/>
@@ -2518,7 +2517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -2672,7 +2671,7 @@
       <c r="J8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="34"/>
@@ -2698,7 +2697,7 @@
       <c r="J10" s="38"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="18"/>
       <c r="D11" s="34"/>
@@ -2724,7 +2723,7 @@
       <c r="J12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="18"/>
       <c r="D13" s="34"/>
@@ -2750,7 +2749,7 @@
       <c r="J14" s="38"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
       <c r="D15" s="34"/>
@@ -2776,7 +2775,7 @@
       <c r="J16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="18"/>
       <c r="D17" s="34"/>
@@ -2802,7 +2801,7 @@
       <c r="J18" s="38"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="18"/>
       <c r="D19" s="7"/>
@@ -2826,7 +2825,7 @@
       <c r="J20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -3019,7 +3018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -3196,7 +3195,7 @@
       </c>
       <c r="F7" s="67"/>
       <c r="G7" s="67"/>
-      <c r="H7" s="68" t="n"/>
+      <c r="H7" s="68"/>
       <c r="I7" s="59" t="s">
         <v>75</v>
       </c>
@@ -3220,7 +3219,7 @@
       </c>
       <c r="F8" s="67"/>
       <c r="G8" s="67"/>
-      <c r="H8" s="68" t="n"/>
+      <c r="H8" s="68"/>
       <c r="I8" s="59" t="s">
         <v>75</v>
       </c>
@@ -3244,7 +3243,7 @@
       </c>
       <c r="F9" s="67"/>
       <c r="G9" s="67"/>
-      <c r="H9" s="68" t="n"/>
+      <c r="H9" s="68"/>
       <c r="I9" s="59" t="s">
         <v>75</v>
       </c>
@@ -3268,7 +3267,7 @@
       </c>
       <c r="F10" s="67"/>
       <c r="G10" s="67"/>
-      <c r="H10" s="68" t="n"/>
+      <c r="H10" s="68"/>
       <c r="I10" s="59" t="s">
         <v>84</v>
       </c>
@@ -3292,7 +3291,7 @@
       </c>
       <c r="F11" s="67"/>
       <c r="G11" s="67"/>
-      <c r="H11" s="68" t="n"/>
+      <c r="H11" s="68"/>
       <c r="I11" s="59" t="s">
         <v>84</v>
       </c>
@@ -3305,7 +3304,7 @@
       <c r="N11" s="69"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="64" t="n"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="59" t="s">
         <v>29</v>
       </c>
@@ -3316,7 +3315,7 @@
       </c>
       <c r="F12" s="67"/>
       <c r="G12" s="67"/>
-      <c r="H12" s="68" t="n"/>
+      <c r="H12" s="68"/>
       <c r="I12" s="59" t="s">
         <v>89</v>
       </c>
@@ -3329,7 +3328,7 @@
       <c r="N12" s="69"/>
     </row>
     <row r="13" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64" t="n"/>
+      <c r="A13" s="64"/>
       <c r="B13" s="59" t="s">
         <v>75</v>
       </c>
@@ -3340,7 +3339,7 @@
       </c>
       <c r="F13" s="67"/>
       <c r="G13" s="67"/>
-      <c r="H13" s="68" t="n"/>
+      <c r="H13" s="68"/>
       <c r="I13" s="59" t="s">
         <v>91</v>
       </c>
@@ -3353,7 +3352,7 @@
       <c r="N13" s="69"/>
     </row>
     <row r="14" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70" t="n"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="71" t="s">
         <v>75</v>
       </c>
@@ -3364,7 +3363,7 @@
       </c>
       <c r="F14" s="72"/>
       <c r="G14" s="72"/>
-      <c r="H14" s="73" t="n"/>
+      <c r="H14" s="73"/>
       <c r="I14" s="71" t="s">
         <v>94</v>
       </c>
@@ -3471,7 +3470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>

--- a/construction_template/data/templates_blank/test_control.xlsx
+++ b/construction_template/data/templates_blank/test_control.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="97">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">材料設備送審管制總表</t>
@@ -56,7 +56,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
   </si>
   <si>
@@ -492,7 +492,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">工程名稱</t>
@@ -612,7 +612,7 @@
     <t xml:space="preserve">契約編號</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">竣工日期</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">監造單位</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">施工廠商</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">施工抽查項目</t>

--- a/construction_template/data/templates_blank/test_control.xlsx
+++ b/construction_template/data/templates_blank/test_control.xlsx
@@ -48,15 +48,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造單位：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/test_control.xlsx
+++ b/construction_template/data/templates_blank/test_control.xlsx
@@ -44,7 +44,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造單位：</t>
@@ -66,7 +66,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否取樣試驗
@@ -84,7 +84,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
@@ -109,7 +109,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">備註</t>
@@ -126,7 +126,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">歸檔編號</t>
@@ -163,7 +163,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">材料</t>
@@ -180,7 +180,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設備</t>
@@ -197,7 +197,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">名稱</t>
@@ -223,7 +223,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">鋼筋，</t>
@@ -270,7 +270,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商應依契約之「材料、設備檢（試）驗一覽表」將資料填入，以預為準備材料設備送審事宜，並作為監造單位管制各項材料設備送審期程</t>
@@ -279,7 +279,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，且需納入結算書陳核。</t>
@@ -298,7 +298,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商應將本表於開工報核時檢附提供予監造單位，監造單位報核開工時應檢附本表。</t>
@@ -317,7 +317,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商應於開工後適時更新本表，並提送監造單位審核，以確認各項材料設備送審期程是否符合時程。</t>
@@ -357,7 +357,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編製：</t>
@@ -366,7 +366,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFFCC99"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -385,7 +385,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">本表於施工期間監造單位依契約約定之「材料、設備送審文件、樣品一覽表」分類登錄，俾利控管材料檢驗使用情形。</t>
@@ -404,7 +404,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造單位應依監造計畫之材料設備抽驗程序及標準辦理材料設備抽驗，如有單項材料設備廠商自主檢查頻率未達 </t>
@@ -421,7 +421,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">次時，廠商在辦理自主檢查取樣前，應通知監造單位轉知考工單位會同廠商辦理抽驗（即前</t>
@@ -438,7 +438,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">次均由本處派員抽驗）。</t>
@@ -457,7 +457,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">本表規定檢驗頻率請依據工程契約或施工規範約定填寫。</t>
@@ -476,7 +476,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">歸檔編號欄位填寫簽奉核准日或發文日期。</t>
@@ -493,7 +493,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">和平東路</t>
@@ -512,7 +512,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">段</t>
@@ -531,7 +531,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">巷兩側側溝更新工程</t>
@@ -555,7 +555,7 @@
       <rPr>
         <sz val="16"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年</t>
@@ -574,7 +574,7 @@
       <rPr>
         <sz val="16"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -593,7 +593,7 @@
       <rPr>
         <sz val="16"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日</t>
@@ -623,7 +623,7 @@
       <rPr>
         <sz val="16"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年</t>
@@ -642,7 +642,7 @@
       <rPr>
         <sz val="16"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -661,7 +661,7 @@
       <rPr>
         <sz val="16"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日</t>
@@ -773,7 +773,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">備註：依</t>
@@ -790,7 +790,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年</t>
@@ -807,7 +807,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月</t>
@@ -824,7 +824,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日臺北市工務局工程會報</t>
@@ -841,7 +841,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">局務會議</t>
@@ -858,7 +858,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">及技師法第</t>
@@ -875,7 +875,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">條規定辦理</t>
@@ -924,24 +924,24 @@
     <font>
       <b val="true"/>
       <sz val="18"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -989,7 +989,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -1010,7 +1010,7 @@
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -1036,28 +1036,28 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFFCC99"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -1077,7 +1077,7 @@
     <font>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -1109,7 +1109,7 @@
     </font>
     <font>
       <sz val="18"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
   </fonts>
